--- a/api/src/excelreports/reportTemplates/Contacts.xlsx
+++ b/api/src/excelreports/reportTemplates/Contacts.xlsx
@@ -145,9 +145,6 @@
     <t>State</t>
   </si>
   <si>
-    <t>Country</t>
-  </si>
-  <si>
     <t>Tags</t>
   </si>
   <si>
@@ -161,6 +158,9 @@
   </si>
   <si>
     <t>&lt;tags&gt;</t>
+  </si>
+  <si>
+    <t>County</t>
   </si>
 </sst>
 </file>
@@ -832,10 +832,10 @@
         <v>40</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -843,16 +843,16 @@
         <v>33</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="11" t="s">
         <v>45</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
